--- a/docs/downloads/11/tbl_cultures_touchees_marovoay_bepako.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_marovoay_bepako.xlsx
@@ -513,12 +513,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +525,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +537,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +549,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -585,12 +561,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +573,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +585,6 @@
           <t>patate douce</t>
         </is>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +597,6 @@
           <t>Aubergine</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -656,12 +608,6 @@
         <is>
           <t>Autres légumes</t>
         </is>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>2.3</v>
       </c>
     </row>
   </sheetData>
